--- a/output/SB_DWH_PDTD_DTM_Lineage.xlsx
+++ b/output/SB_DWH_PDTD_DTM_Lineage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiennguyen/sb-mapping-gen/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9785E3B7-21FE-2841-94AA-205AC7537CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871C3319-3133-C847-9BD1-3AA610826384}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16860" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS Bảng" sheetId="1" r:id="rId1"/>
@@ -28797,6 +28797,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K713"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
@@ -29013,7 +29014,7 @@
       </c>
       <c r="K6" s="16"/>
     </row>
-    <row r="7" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="16">
         <v>696</v>
       </c>
@@ -29044,7 +29045,7 @@
       </c>
       <c r="K7" s="16"/>
     </row>
-    <row r="8" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="16">
         <v>697</v>
       </c>
@@ -29075,7 +29076,7 @@
       </c>
       <c r="K8" s="16"/>
     </row>
-    <row r="9" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="16">
         <v>698</v>
       </c>
@@ -29106,7 +29107,7 @@
       </c>
       <c r="K9" s="16"/>
     </row>
-    <row r="10" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="16">
         <v>699</v>
       </c>
@@ -29137,7 +29138,7 @@
       </c>
       <c r="K10" s="16"/>
     </row>
-    <row r="11" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="16">
         <v>700</v>
       </c>
@@ -29168,7 +29169,7 @@
       </c>
       <c r="K11" s="16"/>
     </row>
-    <row r="12" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="16">
         <v>701</v>
       </c>
@@ -29199,7 +29200,7 @@
       </c>
       <c r="K12" s="16"/>
     </row>
-    <row r="13" spans="1:11" ht="394.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" ht="394.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="16">
         <v>702</v>
       </c>
@@ -29230,7 +29231,7 @@
       </c>
       <c r="K13" s="16"/>
     </row>
-    <row r="14" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="16">
         <v>703</v>
       </c>
@@ -29261,7 +29262,7 @@
       </c>
       <c r="K14" s="16"/>
     </row>
-    <row r="15" spans="1:11" ht="379.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:11" ht="379.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="16">
         <v>704</v>
       </c>
@@ -29292,7 +29293,7 @@
       </c>
       <c r="K15" s="16"/>
     </row>
-    <row r="16" spans="1:11" ht="255.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:11" ht="255.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="16">
         <v>705</v>
       </c>
@@ -29323,7 +29324,7 @@
       </c>
       <c r="K16" s="16"/>
     </row>
-    <row r="17" spans="1:11" ht="223.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:11" ht="223.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="16">
         <v>706</v>
       </c>
@@ -29354,7 +29355,7 @@
       </c>
       <c r="K17" s="16"/>
     </row>
-    <row r="18" spans="1:11" ht="223.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:11" ht="223.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="16">
         <v>707</v>
       </c>
@@ -29385,7 +29386,7 @@
       </c>
       <c r="K18" s="16"/>
     </row>
-    <row r="19" spans="1:11" ht="288" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:11" ht="288" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="16">
         <v>708</v>
       </c>
@@ -29416,7 +29417,7 @@
       </c>
       <c r="K19" s="16"/>
     </row>
-    <row r="20" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="16">
         <v>709</v>
       </c>
@@ -29447,7 +29448,7 @@
       </c>
       <c r="K20" s="16"/>
     </row>
-    <row r="21" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="16">
         <v>710</v>
       </c>
@@ -29478,7 +29479,7 @@
       </c>
       <c r="K21" s="16"/>
     </row>
-    <row r="22" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="16">
         <v>711</v>
       </c>
@@ -29509,7 +29510,7 @@
       </c>
       <c r="K22" s="16"/>
     </row>
-    <row r="23" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="16">
         <v>712</v>
       </c>
@@ -29542,7 +29543,7 @@
         <v>3496</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="16">
         <v>713</v>
       </c>
@@ -29575,7 +29576,7 @@
         <v>3501</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="16">
         <v>714</v>
       </c>
@@ -29608,7 +29609,7 @@
         <v>3504</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="255.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:11" ht="255.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="16">
         <v>715</v>
       </c>
@@ -29641,7 +29642,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="16">
         <v>716</v>
       </c>
@@ -29674,7 +29675,7 @@
         <v>3507</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="16">
         <v>717</v>
       </c>
@@ -29952,7 +29953,7 @@
         <v>3450</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="16">
         <v>684</v>
       </c>
@@ -29983,7 +29984,7 @@
       </c>
       <c r="K36" s="16"/>
     </row>
-    <row r="37" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="16">
         <v>685</v>
       </c>
@@ -30016,7 +30017,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="16">
         <v>686</v>
       </c>
@@ -30049,7 +30050,7 @@
         <v>3456</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="16">
         <v>687</v>
       </c>
@@ -30080,7 +30081,7 @@
       </c>
       <c r="K39" s="16"/>
     </row>
-    <row r="40" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="16">
         <v>688</v>
       </c>
@@ -30113,7 +30114,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="288" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:11" ht="288" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="16">
         <v>689</v>
       </c>
@@ -30146,7 +30147,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="16">
         <v>690</v>
       </c>
@@ -30346,7 +30347,7 @@
       </c>
       <c r="K47" s="16"/>
     </row>
-    <row r="48" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="16">
         <v>666</v>
       </c>
@@ -30377,7 +30378,7 @@
       </c>
       <c r="K48" s="16"/>
     </row>
-    <row r="49" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="16">
         <v>667</v>
       </c>
@@ -30408,7 +30409,7 @@
       </c>
       <c r="K49" s="16"/>
     </row>
-    <row r="50" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="16">
         <v>668</v>
       </c>
@@ -30439,7 +30440,7 @@
       </c>
       <c r="K50" s="16"/>
     </row>
-    <row r="51" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16">
         <v>669</v>
       </c>
@@ -30470,7 +30471,7 @@
       </c>
       <c r="K51" s="16"/>
     </row>
-    <row r="52" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="16">
         <v>670</v>
       </c>
@@ -30501,7 +30502,7 @@
       </c>
       <c r="K52" s="16"/>
     </row>
-    <row r="53" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="16">
         <v>671</v>
       </c>
@@ -30532,7 +30533,7 @@
       </c>
       <c r="K53" s="16"/>
     </row>
-    <row r="54" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="16">
         <v>672</v>
       </c>
@@ -30563,7 +30564,7 @@
       </c>
       <c r="K54" s="16"/>
     </row>
-    <row r="55" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="16">
         <v>673</v>
       </c>
@@ -30594,7 +30595,7 @@
       </c>
       <c r="K55" s="16"/>
     </row>
-    <row r="56" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="16">
         <v>674</v>
       </c>
@@ -30627,7 +30628,7 @@
         <v>3423</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="16">
         <v>675</v>
       </c>
@@ -30660,7 +30661,7 @@
         <v>3427</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="16">
         <v>676</v>
       </c>
@@ -30794,7 +30795,7 @@
       </c>
       <c r="K61" s="16"/>
     </row>
-    <row r="62" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="16">
         <v>656</v>
       </c>
@@ -30825,7 +30826,7 @@
       </c>
       <c r="K62" s="16"/>
     </row>
-    <row r="63" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="16">
         <v>657</v>
       </c>
@@ -30856,7 +30857,7 @@
       </c>
       <c r="K63" s="16"/>
     </row>
-    <row r="64" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="16">
         <v>658</v>
       </c>
@@ -30887,7 +30888,7 @@
       </c>
       <c r="K64" s="16"/>
     </row>
-    <row r="65" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="16">
         <v>659</v>
       </c>
@@ -30918,7 +30919,7 @@
       </c>
       <c r="K65" s="16"/>
     </row>
-    <row r="66" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="16">
         <v>660</v>
       </c>
@@ -31085,7 +31086,7 @@
         <v>3355</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="16">
         <v>621</v>
       </c>
@@ -31116,7 +31117,7 @@
       </c>
       <c r="K71" s="16"/>
     </row>
-    <row r="72" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="16">
         <v>622</v>
       </c>
@@ -31147,7 +31148,7 @@
       </c>
       <c r="K72" s="16"/>
     </row>
-    <row r="73" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="16">
         <v>623</v>
       </c>
@@ -31178,7 +31179,7 @@
       </c>
       <c r="K73" s="16"/>
     </row>
-    <row r="74" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="16">
         <v>624</v>
       </c>
@@ -31209,7 +31210,7 @@
       </c>
       <c r="K74" s="16"/>
     </row>
-    <row r="75" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="16">
         <v>625</v>
       </c>
@@ -31240,7 +31241,7 @@
       </c>
       <c r="K75" s="16"/>
     </row>
-    <row r="76" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="16">
         <v>626</v>
       </c>
@@ -31271,7 +31272,7 @@
       </c>
       <c r="K76" s="16"/>
     </row>
-    <row r="77" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="16">
         <v>627</v>
       </c>
@@ -31302,7 +31303,7 @@
       </c>
       <c r="K77" s="16"/>
     </row>
-    <row r="78" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="16">
         <v>628</v>
       </c>
@@ -31333,7 +31334,7 @@
       </c>
       <c r="K78" s="16"/>
     </row>
-    <row r="79" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="16">
         <v>629</v>
       </c>
@@ -31364,7 +31365,7 @@
       </c>
       <c r="K79" s="16"/>
     </row>
-    <row r="80" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="16">
         <v>630</v>
       </c>
@@ -31395,7 +31396,7 @@
       </c>
       <c r="K80" s="16"/>
     </row>
-    <row r="81" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="16">
         <v>631</v>
       </c>
@@ -31426,7 +31427,7 @@
       </c>
       <c r="K81" s="16"/>
     </row>
-    <row r="82" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="16">
         <v>632</v>
       </c>
@@ -31457,7 +31458,7 @@
       </c>
       <c r="K82" s="16"/>
     </row>
-    <row r="83" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="16">
         <v>633</v>
       </c>
@@ -31488,7 +31489,7 @@
       </c>
       <c r="K83" s="16"/>
     </row>
-    <row r="84" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="16">
         <v>634</v>
       </c>
@@ -31519,7 +31520,7 @@
       </c>
       <c r="K84" s="16"/>
     </row>
-    <row r="85" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="16">
         <v>635</v>
       </c>
@@ -31550,7 +31551,7 @@
       </c>
       <c r="K85" s="16"/>
     </row>
-    <row r="86" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="16">
         <v>636</v>
       </c>
@@ -31581,7 +31582,7 @@
       </c>
       <c r="K86" s="16"/>
     </row>
-    <row r="87" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="16">
         <v>637</v>
       </c>
@@ -31612,7 +31613,7 @@
       </c>
       <c r="K87" s="16"/>
     </row>
-    <row r="88" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="16">
         <v>638</v>
       </c>
@@ -31643,7 +31644,7 @@
       </c>
       <c r="K88" s="16"/>
     </row>
-    <row r="89" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="16">
         <v>639</v>
       </c>
@@ -31674,7 +31675,7 @@
       </c>
       <c r="K89" s="16"/>
     </row>
-    <row r="90" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="16">
         <v>640</v>
       </c>
@@ -31705,7 +31706,7 @@
       </c>
       <c r="K90" s="16"/>
     </row>
-    <row r="91" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="16">
         <v>641</v>
       </c>
@@ -31736,7 +31737,7 @@
       </c>
       <c r="K91" s="16"/>
     </row>
-    <row r="92" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="16">
         <v>642</v>
       </c>
@@ -31767,7 +31768,7 @@
       </c>
       <c r="K92" s="16"/>
     </row>
-    <row r="93" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="16">
         <v>643</v>
       </c>
@@ -31798,7 +31799,7 @@
       </c>
       <c r="K93" s="16"/>
     </row>
-    <row r="94" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="16">
         <v>644</v>
       </c>
@@ -31829,7 +31830,7 @@
       </c>
       <c r="K94" s="16"/>
     </row>
-    <row r="95" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="16">
         <v>645</v>
       </c>
@@ -31860,7 +31861,7 @@
       </c>
       <c r="K95" s="16"/>
     </row>
-    <row r="96" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="16">
         <v>646</v>
       </c>
@@ -31891,7 +31892,7 @@
       </c>
       <c r="K96" s="16"/>
     </row>
-    <row r="97" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="16">
         <v>647</v>
       </c>
@@ -31922,7 +31923,7 @@
       </c>
       <c r="K97" s="16"/>
     </row>
-    <row r="98" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="16">
         <v>648</v>
       </c>
@@ -31953,7 +31954,7 @@
       </c>
       <c r="K98" s="16"/>
     </row>
-    <row r="99" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="16">
         <v>649</v>
       </c>
@@ -31984,7 +31985,7 @@
       </c>
       <c r="K99" s="16"/>
     </row>
-    <row r="100" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="16">
         <v>650</v>
       </c>
@@ -32015,7 +32016,7 @@
       </c>
       <c r="K100" s="16"/>
     </row>
-    <row r="101" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="16">
         <v>651</v>
       </c>
@@ -32046,7 +32047,7 @@
       </c>
       <c r="K101" s="16"/>
     </row>
-    <row r="102" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="16">
         <v>652</v>
       </c>
@@ -32178,7 +32179,7 @@
       </c>
       <c r="K105" s="16"/>
     </row>
-    <row r="106" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="16">
         <v>604</v>
       </c>
@@ -32209,7 +32210,7 @@
       </c>
       <c r="K106" s="16"/>
     </row>
-    <row r="107" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="16">
         <v>605</v>
       </c>
@@ -32240,7 +32241,7 @@
       </c>
       <c r="K107" s="16"/>
     </row>
-    <row r="108" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="16">
         <v>606</v>
       </c>
@@ -32271,7 +32272,7 @@
       </c>
       <c r="K108" s="16"/>
     </row>
-    <row r="109" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="16">
         <v>607</v>
       </c>
@@ -32302,7 +32303,7 @@
       </c>
       <c r="K109" s="16"/>
     </row>
-    <row r="110" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="16">
         <v>608</v>
       </c>
@@ -32333,7 +32334,7 @@
       </c>
       <c r="K110" s="16"/>
     </row>
-    <row r="111" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="16">
         <v>609</v>
       </c>
@@ -32364,7 +32365,7 @@
       </c>
       <c r="K111" s="16"/>
     </row>
-    <row r="112" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="16">
         <v>610</v>
       </c>
@@ -32395,7 +32396,7 @@
       </c>
       <c r="K112" s="16"/>
     </row>
-    <row r="113" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:11" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="16">
         <v>611</v>
       </c>
@@ -32426,7 +32427,7 @@
       </c>
       <c r="K113" s="16"/>
     </row>
-    <row r="114" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="16">
         <v>612</v>
       </c>
@@ -32457,7 +32458,7 @@
       </c>
       <c r="K114" s="16"/>
     </row>
-    <row r="115" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="16">
         <v>613</v>
       </c>
@@ -32488,7 +32489,7 @@
       </c>
       <c r="K115" s="16"/>
     </row>
-    <row r="116" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="16">
         <v>614</v>
       </c>
@@ -32519,7 +32520,7 @@
       </c>
       <c r="K116" s="16"/>
     </row>
-    <row r="117" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="16">
         <v>615</v>
       </c>
@@ -32550,7 +32551,7 @@
       </c>
       <c r="K117" s="16"/>
     </row>
-    <row r="118" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="16">
         <v>616</v>
       </c>
@@ -32682,7 +32683,7 @@
       </c>
       <c r="K121" s="16"/>
     </row>
-    <row r="122" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="16">
         <v>586</v>
       </c>
@@ -32713,7 +32714,7 @@
       </c>
       <c r="K122" s="16"/>
     </row>
-    <row r="123" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="16">
         <v>587</v>
       </c>
@@ -32744,7 +32745,7 @@
       </c>
       <c r="K123" s="16"/>
     </row>
-    <row r="124" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="16">
         <v>588</v>
       </c>
@@ -32775,7 +32776,7 @@
       </c>
       <c r="K124" s="16"/>
     </row>
-    <row r="125" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="16">
         <v>589</v>
       </c>
@@ -32806,7 +32807,7 @@
       </c>
       <c r="K125" s="16"/>
     </row>
-    <row r="126" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="16">
         <v>590</v>
       </c>
@@ -32837,7 +32838,7 @@
       </c>
       <c r="K126" s="16"/>
     </row>
-    <row r="127" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="16">
         <v>591</v>
       </c>
@@ -32868,7 +32869,7 @@
       </c>
       <c r="K127" s="16"/>
     </row>
-    <row r="128" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="16">
         <v>592</v>
       </c>
@@ -32899,7 +32900,7 @@
       </c>
       <c r="K128" s="16"/>
     </row>
-    <row r="129" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="16">
         <v>593</v>
       </c>
@@ -32930,7 +32931,7 @@
       </c>
       <c r="K129" s="16"/>
     </row>
-    <row r="130" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="16">
         <v>594</v>
       </c>
@@ -32961,7 +32962,7 @@
       </c>
       <c r="K130" s="16"/>
     </row>
-    <row r="131" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="16">
         <v>595</v>
       </c>
@@ -32992,7 +32993,7 @@
       </c>
       <c r="K131" s="16"/>
     </row>
-    <row r="132" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="16">
         <v>596</v>
       </c>
@@ -33023,7 +33024,7 @@
       </c>
       <c r="K132" s="16"/>
     </row>
-    <row r="133" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="16">
         <v>597</v>
       </c>
@@ -33054,7 +33055,7 @@
       </c>
       <c r="K133" s="16"/>
     </row>
-    <row r="134" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="16">
         <v>598</v>
       </c>
@@ -33085,7 +33086,7 @@
       </c>
       <c r="K134" s="16"/>
     </row>
-    <row r="135" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="16">
         <v>599</v>
       </c>
@@ -33116,7 +33117,7 @@
       </c>
       <c r="K135" s="16"/>
     </row>
-    <row r="136" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="16">
         <v>600</v>
       </c>
@@ -33283,7 +33284,7 @@
         <v>3278</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="16">
         <v>578</v>
       </c>
@@ -33314,7 +33315,7 @@
       </c>
       <c r="K141" s="16"/>
     </row>
-    <row r="142" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="16">
         <v>579</v>
       </c>
@@ -33345,7 +33346,7 @@
       </c>
       <c r="K142" s="16"/>
     </row>
-    <row r="143" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="16">
         <v>580</v>
       </c>
@@ -33376,7 +33377,7 @@
       </c>
       <c r="K143" s="16"/>
     </row>
-    <row r="144" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="16">
         <v>581</v>
       </c>
@@ -33407,7 +33408,7 @@
       </c>
       <c r="K144" s="16"/>
     </row>
-    <row r="145" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="16">
         <v>582</v>
       </c>
@@ -33809,7 +33810,7 @@
         <v>3169</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="16">
         <v>535</v>
       </c>
@@ -33840,7 +33841,7 @@
       </c>
       <c r="K157" s="16"/>
     </row>
-    <row r="158" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="16">
         <v>536</v>
       </c>
@@ -33871,7 +33872,7 @@
       </c>
       <c r="K158" s="16"/>
     </row>
-    <row r="159" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="16">
         <v>537</v>
       </c>
@@ -33902,7 +33903,7 @@
       </c>
       <c r="K159" s="16"/>
     </row>
-    <row r="160" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="16">
         <v>538</v>
       </c>
@@ -33933,7 +33934,7 @@
       </c>
       <c r="K160" s="16"/>
     </row>
-    <row r="161" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="16">
         <v>539</v>
       </c>
@@ -33964,7 +33965,7 @@
       </c>
       <c r="K161" s="16"/>
     </row>
-    <row r="162" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="16">
         <v>540</v>
       </c>
@@ -33995,7 +33996,7 @@
       </c>
       <c r="K162" s="16"/>
     </row>
-    <row r="163" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="16">
         <v>541</v>
       </c>
@@ -34026,7 +34027,7 @@
       </c>
       <c r="K163" s="16"/>
     </row>
-    <row r="164" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="16">
         <v>542</v>
       </c>
@@ -34057,7 +34058,7 @@
       </c>
       <c r="K164" s="16"/>
     </row>
-    <row r="165" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="16">
         <v>543</v>
       </c>
@@ -34088,7 +34089,7 @@
       </c>
       <c r="K165" s="16"/>
     </row>
-    <row r="166" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="16">
         <v>544</v>
       </c>
@@ -34121,7 +34122,7 @@
         <v>3183</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="16">
         <v>545</v>
       </c>
@@ -34152,7 +34153,7 @@
       </c>
       <c r="K167" s="16"/>
     </row>
-    <row r="168" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="16">
         <v>546</v>
       </c>
@@ -34183,7 +34184,7 @@
       </c>
       <c r="K168" s="16"/>
     </row>
-    <row r="169" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="16">
         <v>547</v>
       </c>
@@ -34216,7 +34217,7 @@
         <v>3191</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="16">
         <v>548</v>
       </c>
@@ -34249,7 +34250,7 @@
         <v>3193</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="16">
         <v>549</v>
       </c>
@@ -34280,7 +34281,7 @@
       </c>
       <c r="K171" s="16"/>
     </row>
-    <row r="172" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="16">
         <v>550</v>
       </c>
@@ -34313,7 +34314,7 @@
         <v>3196</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="16">
         <v>551</v>
       </c>
@@ -34344,7 +34345,7 @@
       </c>
       <c r="K173" s="16"/>
     </row>
-    <row r="174" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="16">
         <v>552</v>
       </c>
@@ -34377,7 +34378,7 @@
         <v>3199</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="16">
         <v>553</v>
       </c>
@@ -34408,7 +34409,7 @@
       </c>
       <c r="K175" s="16"/>
     </row>
-    <row r="176" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="16">
         <v>554</v>
       </c>
@@ -34441,7 +34442,7 @@
         <v>3208</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="16">
         <v>555</v>
       </c>
@@ -34472,7 +34473,7 @@
       </c>
       <c r="K177" s="16"/>
     </row>
-    <row r="178" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="16">
         <v>556</v>
       </c>
@@ -34503,7 +34504,7 @@
       </c>
       <c r="K178" s="16"/>
     </row>
-    <row r="179" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="16">
         <v>557</v>
       </c>
@@ -34536,7 +34537,7 @@
         <v>3215</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="16">
         <v>558</v>
       </c>
@@ -34569,7 +34570,7 @@
         <v>3218</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" ht="102.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="16">
         <v>559</v>
       </c>
@@ -34602,7 +34603,7 @@
         <v>3221</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="16">
         <v>560</v>
       </c>
@@ -34635,7 +34636,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="16">
         <v>561</v>
       </c>
@@ -34666,7 +34667,7 @@
       </c>
       <c r="K183" s="16"/>
     </row>
-    <row r="184" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="16">
         <v>562</v>
       </c>
@@ -34697,7 +34698,7 @@
       </c>
       <c r="K184" s="16"/>
     </row>
-    <row r="185" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="16">
         <v>563</v>
       </c>
@@ -34730,7 +34731,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="16">
         <v>564</v>
       </c>
@@ -34763,7 +34764,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="187" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="16">
         <v>565</v>
       </c>
@@ -34796,7 +34797,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="188" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="16">
         <v>566</v>
       </c>
@@ -34827,7 +34828,7 @@
       </c>
       <c r="K188" s="16"/>
     </row>
-    <row r="189" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="16">
         <v>567</v>
       </c>
@@ -34858,7 +34859,7 @@
       </c>
       <c r="K189" s="16"/>
     </row>
-    <row r="190" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="16">
         <v>568</v>
       </c>
@@ -34891,7 +34892,7 @@
         <v>3255</v>
       </c>
     </row>
-    <row r="191" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="16">
         <v>569</v>
       </c>
@@ -34924,7 +34925,7 @@
         <v>3259</v>
       </c>
     </row>
-    <row r="192" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="16">
         <v>570</v>
       </c>
@@ -34955,7 +34956,7 @@
       </c>
       <c r="K192" s="16"/>
     </row>
-    <row r="193" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="16">
         <v>571</v>
       </c>
@@ -34986,7 +34987,7 @@
       </c>
       <c r="K193" s="16"/>
     </row>
-    <row r="194" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="16">
         <v>572</v>
       </c>
@@ -35017,7 +35018,7 @@
       </c>
       <c r="K194" s="16"/>
     </row>
-    <row r="195" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="16">
         <v>573</v>
       </c>
@@ -35248,7 +35249,7 @@
       </c>
       <c r="K201" s="16"/>
     </row>
-    <row r="202" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="16">
         <v>503</v>
       </c>
@@ -35279,7 +35280,7 @@
       </c>
       <c r="K202" s="16"/>
     </row>
-    <row r="203" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="16">
         <v>504</v>
       </c>
@@ -35310,7 +35311,7 @@
       </c>
       <c r="K203" s="16"/>
     </row>
-    <row r="204" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="16">
         <v>505</v>
       </c>
@@ -35341,7 +35342,7 @@
       </c>
       <c r="K204" s="16"/>
     </row>
-    <row r="205" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="16">
         <v>506</v>
       </c>
@@ -35372,7 +35373,7 @@
       </c>
       <c r="K205" s="16"/>
     </row>
-    <row r="206" spans="1:11" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:11" ht="102.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="16">
         <v>507</v>
       </c>
@@ -35403,7 +35404,7 @@
       </c>
       <c r="K206" s="16"/>
     </row>
-    <row r="207" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="16">
         <v>508</v>
       </c>
@@ -35434,7 +35435,7 @@
       </c>
       <c r="K207" s="16"/>
     </row>
-    <row r="208" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="16">
         <v>509</v>
       </c>
@@ -35465,7 +35466,7 @@
       </c>
       <c r="K208" s="16"/>
     </row>
-    <row r="209" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="16">
         <v>510</v>
       </c>
@@ -35496,7 +35497,7 @@
       </c>
       <c r="K209" s="16"/>
     </row>
-    <row r="210" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="16">
         <v>511</v>
       </c>
@@ -35527,7 +35528,7 @@
       </c>
       <c r="K210" s="16"/>
     </row>
-    <row r="211" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="16">
         <v>512</v>
       </c>
@@ -35558,7 +35559,7 @@
       </c>
       <c r="K211" s="16"/>
     </row>
-    <row r="212" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="16">
         <v>513</v>
       </c>
@@ -35589,7 +35590,7 @@
       </c>
       <c r="K212" s="16"/>
     </row>
-    <row r="213" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="16">
         <v>514</v>
       </c>
@@ -35620,7 +35621,7 @@
       </c>
       <c r="K213" s="16"/>
     </row>
-    <row r="214" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="16">
         <v>515</v>
       </c>
@@ -35651,7 +35652,7 @@
       </c>
       <c r="K214" s="16"/>
     </row>
-    <row r="215" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="16">
         <v>516</v>
       </c>
@@ -35682,7 +35683,7 @@
       </c>
       <c r="K215" s="16"/>
     </row>
-    <row r="216" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="16">
         <v>517</v>
       </c>
@@ -35715,7 +35716,7 @@
         <v>3110</v>
       </c>
     </row>
-    <row r="217" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="16">
         <v>518</v>
       </c>
@@ -35748,7 +35749,7 @@
         <v>3114</v>
       </c>
     </row>
-    <row r="218" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="16">
         <v>519</v>
       </c>
@@ -35781,7 +35782,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="219" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:11" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="16">
         <v>520</v>
       </c>
@@ -35814,7 +35815,7 @@
         <v>3117</v>
       </c>
     </row>
-    <row r="220" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="16">
         <v>521</v>
       </c>
@@ -35847,7 +35848,7 @@
         <v>3122</v>
       </c>
     </row>
-    <row r="221" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="16">
         <v>522</v>
       </c>
@@ -35880,7 +35881,7 @@
         <v>3127</v>
       </c>
     </row>
-    <row r="222" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:11" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="16">
         <v>523</v>
       </c>
@@ -36156,7 +36157,7 @@
         <v>3012</v>
       </c>
     </row>
-    <row r="230" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="16">
         <v>486</v>
       </c>
@@ -36187,7 +36188,7 @@
       </c>
       <c r="K230" s="16"/>
     </row>
-    <row r="231" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="16">
         <v>487</v>
       </c>
@@ -36220,7 +36221,7 @@
         <v>3021</v>
       </c>
     </row>
-    <row r="232" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="16">
         <v>488</v>
       </c>
@@ -36253,7 +36254,7 @@
         <v>3027</v>
       </c>
     </row>
-    <row r="233" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="16">
         <v>489</v>
       </c>
@@ -36284,7 +36285,7 @@
       </c>
       <c r="K233" s="16"/>
     </row>
-    <row r="234" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="16">
         <v>490</v>
       </c>
@@ -36317,7 +36318,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="235" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="16">
         <v>491</v>
       </c>
@@ -36350,7 +36351,7 @@
         <v>3042</v>
       </c>
     </row>
-    <row r="236" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="16">
         <v>492</v>
       </c>
@@ -36383,7 +36384,7 @@
         <v>3048</v>
       </c>
     </row>
-    <row r="237" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="16">
         <v>493</v>
       </c>
@@ -36416,7 +36417,7 @@
         <v>3051</v>
       </c>
     </row>
-    <row r="238" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="16">
         <v>494</v>
       </c>
@@ -36449,7 +36450,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="239" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="16">
         <v>495</v>
       </c>
@@ -36482,7 +36483,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="240" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="16">
         <v>496</v>
       </c>
@@ -36649,7 +36650,7 @@
       </c>
       <c r="K244" s="16"/>
     </row>
-    <row r="245" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="16">
         <v>473</v>
       </c>
@@ -36680,7 +36681,7 @@
       </c>
       <c r="K245" s="16"/>
     </row>
-    <row r="246" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="16">
         <v>474</v>
       </c>
@@ -36711,7 +36712,7 @@
       </c>
       <c r="K246" s="16"/>
     </row>
-    <row r="247" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="16">
         <v>475</v>
       </c>
@@ -36742,7 +36743,7 @@
       </c>
       <c r="K247" s="16"/>
     </row>
-    <row r="248" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="16">
         <v>476</v>
       </c>
@@ -36773,7 +36774,7 @@
       </c>
       <c r="K248" s="16"/>
     </row>
-    <row r="249" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="16">
         <v>477</v>
       </c>
@@ -36804,7 +36805,7 @@
       </c>
       <c r="K249" s="16"/>
     </row>
-    <row r="250" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="16">
         <v>478</v>
       </c>
@@ -37037,7 +37038,7 @@
       </c>
       <c r="K256" s="16"/>
     </row>
-    <row r="257" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="16">
         <v>459</v>
       </c>
@@ -37068,7 +37069,7 @@
       </c>
       <c r="K257" s="16"/>
     </row>
-    <row r="258" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="16">
         <v>460</v>
       </c>
@@ -37099,7 +37100,7 @@
       </c>
       <c r="K258" s="16"/>
     </row>
-    <row r="259" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="16">
         <v>461</v>
       </c>
@@ -37130,7 +37131,7 @@
       </c>
       <c r="K259" s="16"/>
     </row>
-    <row r="260" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="16">
         <v>462</v>
       </c>
@@ -37161,7 +37162,7 @@
       </c>
       <c r="K260" s="16"/>
     </row>
-    <row r="261" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="16">
         <v>463</v>
       </c>
@@ -37192,7 +37193,7 @@
       </c>
       <c r="K261" s="16"/>
     </row>
-    <row r="262" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="16">
         <v>464</v>
       </c>
@@ -37223,7 +37224,7 @@
       </c>
       <c r="K262" s="16"/>
     </row>
-    <row r="263" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="16">
         <v>465</v>
       </c>
@@ -37254,7 +37255,7 @@
       </c>
       <c r="K263" s="16"/>
     </row>
-    <row r="264" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="16">
         <v>466</v>
       </c>
@@ -37287,7 +37288,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="265" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="16">
         <v>467</v>
       </c>
@@ -37320,7 +37321,7 @@
         <v>2952</v>
       </c>
     </row>
-    <row r="266" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="16">
         <v>468</v>
       </c>
@@ -37454,7 +37455,7 @@
       </c>
       <c r="K269" s="16"/>
     </row>
-    <row r="270" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="16">
         <v>448</v>
       </c>
@@ -37485,7 +37486,7 @@
       </c>
       <c r="K270" s="16"/>
     </row>
-    <row r="271" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="16">
         <v>449</v>
       </c>
@@ -37516,7 +37517,7 @@
       </c>
       <c r="K271" s="16"/>
     </row>
-    <row r="272" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="16">
         <v>450</v>
       </c>
@@ -37547,7 +37548,7 @@
       </c>
       <c r="K272" s="16"/>
     </row>
-    <row r="273" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="16">
         <v>451</v>
       </c>
@@ -37578,7 +37579,7 @@
       </c>
       <c r="K273" s="16"/>
     </row>
-    <row r="274" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="16">
         <v>452</v>
       </c>
@@ -37710,7 +37711,7 @@
       </c>
       <c r="K277" s="16"/>
     </row>
-    <row r="278" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="16">
         <v>438</v>
       </c>
@@ -37743,7 +37744,7 @@
         <v>2895</v>
       </c>
     </row>
-    <row r="279" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="16">
         <v>439</v>
       </c>
@@ -37774,7 +37775,7 @@
       </c>
       <c r="K279" s="16"/>
     </row>
-    <row r="280" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="16">
         <v>440</v>
       </c>
@@ -37805,7 +37806,7 @@
       </c>
       <c r="K280" s="16"/>
     </row>
-    <row r="281" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="16">
         <v>441</v>
       </c>
@@ -37836,7 +37837,7 @@
       </c>
       <c r="K281" s="16"/>
     </row>
-    <row r="282" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="16">
         <v>442</v>
       </c>
@@ -37867,7 +37868,7 @@
       </c>
       <c r="K282" s="16"/>
     </row>
-    <row r="283" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="16">
         <v>443</v>
       </c>
@@ -37898,7 +37899,7 @@
       </c>
       <c r="K283" s="16"/>
     </row>
-    <row r="284" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="16">
         <v>444</v>
       </c>
@@ -38228,7 +38229,7 @@
       </c>
       <c r="K293" s="16"/>
     </row>
-    <row r="294" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="16">
         <v>387</v>
       </c>
@@ -38261,7 +38262,7 @@
         <v>2701</v>
       </c>
     </row>
-    <row r="295" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="16">
         <v>388</v>
       </c>
@@ -38294,7 +38295,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="296" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="16">
         <v>389</v>
       </c>
@@ -38327,7 +38328,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="297" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="16">
         <v>390</v>
       </c>
@@ -38360,7 +38361,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="298" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="16">
         <v>391</v>
       </c>
@@ -38393,7 +38394,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="299" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="16">
         <v>392</v>
       </c>
@@ -38426,7 +38427,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="300" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="16">
         <v>393</v>
       </c>
@@ -38459,7 +38460,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="301" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="16">
         <v>394</v>
       </c>
@@ -38492,7 +38493,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="302" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="16">
         <v>395</v>
       </c>
@@ -38525,7 +38526,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="303" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="16">
         <v>396</v>
       </c>
@@ -38558,7 +38559,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="304" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="16">
         <v>397</v>
       </c>
@@ -38591,7 +38592,7 @@
         <v>2706</v>
       </c>
     </row>
-    <row r="305" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="16">
         <v>398</v>
       </c>
@@ -38622,7 +38623,7 @@
       </c>
       <c r="K305" s="16"/>
     </row>
-    <row r="306" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="16">
         <v>399</v>
       </c>
@@ -38655,7 +38656,7 @@
         <v>2749</v>
       </c>
     </row>
-    <row r="307" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:11" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="16">
         <v>400</v>
       </c>
@@ -38688,7 +38689,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="308" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="16">
         <v>401</v>
       </c>
@@ -38721,7 +38722,7 @@
         <v>2754</v>
       </c>
     </row>
-    <row r="309" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="16">
         <v>402</v>
       </c>
@@ -38754,7 +38755,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="310" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="16">
         <v>403</v>
       </c>
@@ -38787,7 +38788,7 @@
         <v>2768</v>
       </c>
     </row>
-    <row r="311" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="16">
         <v>404</v>
       </c>
@@ -38820,7 +38821,7 @@
         <v>2773</v>
       </c>
     </row>
-    <row r="312" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="16">
         <v>405</v>
       </c>
@@ -38853,7 +38854,7 @@
         <v>2778</v>
       </c>
     </row>
-    <row r="313" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="16">
         <v>406</v>
       </c>
@@ -38886,7 +38887,7 @@
         <v>2783</v>
       </c>
     </row>
-    <row r="314" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="16">
         <v>407</v>
       </c>
@@ -38917,7 +38918,7 @@
       </c>
       <c r="K314" s="16"/>
     </row>
-    <row r="315" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="16">
         <v>408</v>
       </c>
@@ -38948,7 +38949,7 @@
       </c>
       <c r="K315" s="16"/>
     </row>
-    <row r="316" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="16">
         <v>409</v>
       </c>
@@ -38979,7 +38980,7 @@
       </c>
       <c r="K316" s="16"/>
     </row>
-    <row r="317" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="16">
         <v>410</v>
       </c>
@@ -39010,7 +39011,7 @@
       </c>
       <c r="K317" s="16"/>
     </row>
-    <row r="318" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="16">
         <v>411</v>
       </c>
@@ -39041,7 +39042,7 @@
       </c>
       <c r="K318" s="16"/>
     </row>
-    <row r="319" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="16">
         <v>412</v>
       </c>
@@ -39072,7 +39073,7 @@
       </c>
       <c r="K319" s="16"/>
     </row>
-    <row r="320" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="16">
         <v>413</v>
       </c>
@@ -39103,7 +39104,7 @@
       </c>
       <c r="K320" s="16"/>
     </row>
-    <row r="321" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="16">
         <v>414</v>
       </c>
@@ -39134,7 +39135,7 @@
       </c>
       <c r="K321" s="16"/>
     </row>
-    <row r="322" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="16">
         <v>415</v>
       </c>
@@ -39167,7 +39168,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="323" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="16">
         <v>416</v>
       </c>
@@ -39200,7 +39201,7 @@
         <v>2807</v>
       </c>
     </row>
-    <row r="324" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="16">
         <v>417</v>
       </c>
@@ -39233,7 +39234,7 @@
         <v>2810</v>
       </c>
     </row>
-    <row r="325" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="16">
         <v>418</v>
       </c>
@@ -39266,7 +39267,7 @@
         <v>2813</v>
       </c>
     </row>
-    <row r="326" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="16">
         <v>419</v>
       </c>
@@ -39299,7 +39300,7 @@
         <v>2813</v>
       </c>
     </row>
-    <row r="327" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="16">
         <v>420</v>
       </c>
@@ -39332,7 +39333,7 @@
         <v>2813</v>
       </c>
     </row>
-    <row r="328" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="16">
         <v>421</v>
       </c>
@@ -39365,7 +39366,7 @@
         <v>2825</v>
       </c>
     </row>
-    <row r="329" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="16">
         <v>422</v>
       </c>
@@ -39398,7 +39399,7 @@
         <v>2830</v>
       </c>
     </row>
-    <row r="330" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="16">
         <v>423</v>
       </c>
@@ -39431,7 +39432,7 @@
         <v>2836</v>
       </c>
     </row>
-    <row r="331" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="16">
         <v>424</v>
       </c>
@@ -39464,7 +39465,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="332" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="16">
         <v>425</v>
       </c>
@@ -39497,7 +39498,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="333" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="16">
         <v>426</v>
       </c>
@@ -39530,7 +39531,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="334" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="16">
         <v>427</v>
       </c>
@@ -39563,7 +39564,7 @@
         <v>2842</v>
       </c>
     </row>
-    <row r="335" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="16">
         <v>428</v>
       </c>
@@ -39596,7 +39597,7 @@
         <v>2860</v>
       </c>
     </row>
-    <row r="336" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="16">
         <v>429</v>
       </c>
@@ -39629,7 +39630,7 @@
         <v>3522</v>
       </c>
     </row>
-    <row r="337" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="16">
         <v>430</v>
       </c>
@@ -39662,7 +39663,7 @@
         <v>2870</v>
       </c>
     </row>
-    <row r="338" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="16">
         <v>431</v>
       </c>
@@ -39695,7 +39696,7 @@
         <v>2875</v>
       </c>
     </row>
-    <row r="339" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="16">
         <v>432</v>
       </c>
@@ -39728,7 +39729,7 @@
         <v>2880</v>
       </c>
     </row>
-    <row r="340" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="16">
         <v>433</v>
       </c>
@@ -39759,7 +39760,7 @@
       </c>
       <c r="K340" s="16"/>
     </row>
-    <row r="341" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="16">
         <v>434</v>
       </c>
@@ -39825,7 +39826,7 @@
         <v>2668</v>
       </c>
     </row>
-    <row r="343" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="16">
         <v>374</v>
       </c>
@@ -39889,7 +39890,7 @@
         <v>2673</v>
       </c>
     </row>
-    <row r="345" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="16">
         <v>376</v>
       </c>
@@ -39922,7 +39923,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="346" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="16">
         <v>377</v>
       </c>
@@ -39990,7 +39991,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="348" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="16">
         <v>368</v>
       </c>
@@ -40054,7 +40055,7 @@
         <v>2657</v>
       </c>
     </row>
-    <row r="350" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="16">
         <v>370</v>
       </c>
@@ -40087,7 +40088,7 @@
         <v>2661</v>
       </c>
     </row>
-    <row r="351" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="16">
         <v>371</v>
       </c>
@@ -40120,7 +40121,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="352" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="16">
         <v>372</v>
       </c>
@@ -40188,7 +40189,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="354" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="16">
         <v>358</v>
       </c>
@@ -40252,7 +40253,7 @@
         <v>2626</v>
       </c>
     </row>
-    <row r="356" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="16">
         <v>360</v>
       </c>
@@ -40285,7 +40286,7 @@
         <v>2630</v>
       </c>
     </row>
-    <row r="357" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="16">
         <v>361</v>
       </c>
@@ -40318,7 +40319,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="358" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="16">
         <v>362</v>
       </c>
@@ -40351,7 +40352,7 @@
         <v>2638</v>
       </c>
     </row>
-    <row r="359" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="16">
         <v>363</v>
       </c>
@@ -40384,7 +40385,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="360" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="16">
         <v>364</v>
       </c>
@@ -40417,7 +40418,7 @@
         <v>2646</v>
       </c>
     </row>
-    <row r="361" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="16">
         <v>365</v>
       </c>
@@ -40450,7 +40451,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="362" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="16">
         <v>366</v>
       </c>
@@ -40518,7 +40519,7 @@
         <v>2594</v>
       </c>
     </row>
-    <row r="364" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="16">
         <v>347</v>
       </c>
@@ -40582,7 +40583,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="366" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="16">
         <v>349</v>
       </c>
@@ -40615,7 +40616,7 @@
         <v>2603</v>
       </c>
     </row>
-    <row r="367" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="16">
         <v>350</v>
       </c>
@@ -40648,7 +40649,7 @@
         <v>2607</v>
       </c>
     </row>
-    <row r="368" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="16">
         <v>351</v>
       </c>
@@ -40681,7 +40682,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="369" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="16">
         <v>352</v>
       </c>
@@ -40712,7 +40713,7 @@
       </c>
       <c r="K369" s="16"/>
     </row>
-    <row r="370" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="16">
         <v>353</v>
       </c>
@@ -40743,7 +40744,7 @@
       </c>
       <c r="K370" s="16"/>
     </row>
-    <row r="371" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="371" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="16">
         <v>354</v>
       </c>
@@ -40776,7 +40777,7 @@
         <v>2616</v>
       </c>
     </row>
-    <row r="372" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="372" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="16">
         <v>355</v>
       </c>
@@ -40809,7 +40810,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="373" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="373" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="16">
         <v>356</v>
       </c>
@@ -40877,7 +40878,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="375" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="16">
         <v>340</v>
       </c>
@@ -40941,7 +40942,7 @@
         <v>2581</v>
       </c>
     </row>
-    <row r="377" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="377" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="16">
         <v>342</v>
       </c>
@@ -40974,7 +40975,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="378" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="378" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="16">
         <v>343</v>
       </c>
@@ -41007,7 +41008,7 @@
         <v>2587</v>
       </c>
     </row>
-    <row r="379" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="379" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="16">
         <v>344</v>
       </c>
@@ -41040,7 +41041,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="380" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="380" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="16">
         <v>345</v>
       </c>
@@ -41108,7 +41109,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="382" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="382" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="16">
         <v>334</v>
       </c>
@@ -41172,7 +41173,7 @@
         <v>2566</v>
       </c>
     </row>
-    <row r="384" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="384" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="16">
         <v>336</v>
       </c>
@@ -41205,7 +41206,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="385" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="16">
         <v>337</v>
       </c>
@@ -41238,7 +41239,7 @@
         <v>2573</v>
       </c>
     </row>
-    <row r="386" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="16">
         <v>338</v>
       </c>
@@ -41306,7 +41307,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="388" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="16">
         <v>326</v>
       </c>
@@ -41337,7 +41338,7 @@
       </c>
       <c r="K388" s="16"/>
     </row>
-    <row r="389" spans="1:11" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:11" ht="102.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="16">
         <v>327</v>
       </c>
@@ -41436,7 +41437,7 @@
       </c>
       <c r="K391" s="16"/>
     </row>
-    <row r="392" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="16">
         <v>330</v>
       </c>
@@ -41467,7 +41468,7 @@
       </c>
       <c r="K392" s="16"/>
     </row>
-    <row r="393" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="16">
         <v>331</v>
       </c>
@@ -41498,7 +41499,7 @@
       </c>
       <c r="K393" s="16"/>
     </row>
-    <row r="394" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="16">
         <v>332</v>
       </c>
@@ -41564,7 +41565,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="396" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="16">
         <v>318</v>
       </c>
@@ -41661,7 +41662,7 @@
       </c>
       <c r="K398" s="16"/>
     </row>
-    <row r="399" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="16">
         <v>321</v>
       </c>
@@ -41725,7 +41726,7 @@
       </c>
       <c r="K400" s="16"/>
     </row>
-    <row r="401" spans="1:11" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:11" ht="102.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="16">
         <v>323</v>
       </c>
@@ -41756,7 +41757,7 @@
       </c>
       <c r="K401" s="16"/>
     </row>
-    <row r="402" spans="1:11" ht="102.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:11" ht="102.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="16">
         <v>324</v>
       </c>
@@ -41822,7 +41823,7 @@
         <v>2519</v>
       </c>
     </row>
-    <row r="404" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="16">
         <v>307</v>
       </c>
@@ -41886,7 +41887,7 @@
       </c>
       <c r="K405" s="16"/>
     </row>
-    <row r="406" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="16">
         <v>309</v>
       </c>
@@ -41917,7 +41918,7 @@
       </c>
       <c r="K406" s="16"/>
     </row>
-    <row r="407" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="16">
         <v>310</v>
       </c>
@@ -41981,7 +41982,7 @@
       </c>
       <c r="K408" s="16"/>
     </row>
-    <row r="409" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="16">
         <v>312</v>
       </c>
@@ -42012,7 +42013,7 @@
       </c>
       <c r="K409" s="16"/>
     </row>
-    <row r="410" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="16">
         <v>313</v>
       </c>
@@ -42043,7 +42044,7 @@
       </c>
       <c r="K410" s="16"/>
     </row>
-    <row r="411" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="411" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="16">
         <v>314</v>
       </c>
@@ -42074,7 +42075,7 @@
       </c>
       <c r="K411" s="16"/>
     </row>
-    <row r="412" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="16">
         <v>315</v>
       </c>
@@ -42105,7 +42106,7 @@
       </c>
       <c r="K412" s="16"/>
     </row>
-    <row r="413" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="16">
         <v>316</v>
       </c>
@@ -42171,7 +42172,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="415" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="16">
         <v>292</v>
       </c>
@@ -42202,7 +42203,7 @@
       </c>
       <c r="K415" s="16"/>
     </row>
-    <row r="416" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="16">
         <v>293</v>
       </c>
@@ -42365,7 +42366,7 @@
       </c>
       <c r="K420" s="16"/>
     </row>
-    <row r="421" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="16">
         <v>298</v>
       </c>
@@ -42396,7 +42397,7 @@
       </c>
       <c r="K421" s="16"/>
     </row>
-    <row r="422" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="16">
         <v>299</v>
       </c>
@@ -42427,7 +42428,7 @@
       </c>
       <c r="K422" s="16"/>
     </row>
-    <row r="423" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:11" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="16">
         <v>300</v>
       </c>
@@ -42458,7 +42459,7 @@
       </c>
       <c r="K423" s="16"/>
     </row>
-    <row r="424" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="16">
         <v>301</v>
       </c>
@@ -42489,7 +42490,7 @@
       </c>
       <c r="K424" s="16"/>
     </row>
-    <row r="425" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="16">
         <v>302</v>
       </c>
@@ -42520,7 +42521,7 @@
       </c>
       <c r="K425" s="16"/>
     </row>
-    <row r="426" spans="1:11" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:11" ht="128.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="16">
         <v>303</v>
       </c>
@@ -42551,7 +42552,7 @@
       </c>
       <c r="K426" s="16"/>
     </row>
-    <row r="427" spans="1:11" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:11" ht="128.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="16">
         <v>304</v>
       </c>
@@ -42582,7 +42583,7 @@
       </c>
       <c r="K427" s="16"/>
     </row>
-    <row r="428" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="16">
         <v>305</v>
       </c>
@@ -42648,7 +42649,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="430" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="16">
         <v>282</v>
       </c>
@@ -42679,7 +42680,7 @@
       </c>
       <c r="K430" s="16"/>
     </row>
-    <row r="431" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="16">
         <v>283</v>
       </c>
@@ -42745,7 +42746,7 @@
       </c>
       <c r="K432" s="16"/>
     </row>
-    <row r="433" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="16">
         <v>285</v>
       </c>
@@ -42809,7 +42810,7 @@
       </c>
       <c r="K434" s="16"/>
     </row>
-    <row r="435" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="16">
         <v>287</v>
       </c>
@@ -42840,7 +42841,7 @@
       </c>
       <c r="K435" s="16"/>
     </row>
-    <row r="436" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="16">
         <v>288</v>
       </c>
@@ -42871,7 +42872,7 @@
       </c>
       <c r="K436" s="16"/>
     </row>
-    <row r="437" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="16">
         <v>289</v>
       </c>
@@ -42902,7 +42903,7 @@
       </c>
       <c r="K437" s="16"/>
     </row>
-    <row r="438" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="16">
         <v>290</v>
       </c>
@@ -42968,7 +42969,7 @@
         <v>2475</v>
       </c>
     </row>
-    <row r="440" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="16">
         <v>273</v>
       </c>
@@ -43032,7 +43033,7 @@
       </c>
       <c r="K441" s="16"/>
     </row>
-    <row r="442" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="16">
         <v>275</v>
       </c>
@@ -43063,7 +43064,7 @@
       </c>
       <c r="K442" s="16"/>
     </row>
-    <row r="443" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="16">
         <v>276</v>
       </c>
@@ -43094,7 +43095,7 @@
       </c>
       <c r="K443" s="16"/>
     </row>
-    <row r="444" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="16">
         <v>277</v>
       </c>
@@ -43125,7 +43126,7 @@
       </c>
       <c r="K444" s="16"/>
     </row>
-    <row r="445" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="16">
         <v>278</v>
       </c>
@@ -43156,7 +43157,7 @@
       </c>
       <c r="K445" s="16"/>
     </row>
-    <row r="446" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="16">
         <v>279</v>
       </c>
@@ -43187,7 +43188,7 @@
       </c>
       <c r="K446" s="16"/>
     </row>
-    <row r="447" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="16">
         <v>280</v>
       </c>
@@ -43253,7 +43254,7 @@
         <v>2390</v>
       </c>
     </row>
-    <row r="449" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="449" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="16">
         <v>209</v>
       </c>
@@ -43317,7 +43318,7 @@
       </c>
       <c r="K450" s="16"/>
     </row>
-    <row r="451" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="451" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="16">
         <v>211</v>
       </c>
@@ -43348,7 +43349,7 @@
       </c>
       <c r="K451" s="16"/>
     </row>
-    <row r="452" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="452" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="16">
         <v>212</v>
       </c>
@@ -43379,7 +43380,7 @@
       </c>
       <c r="K452" s="16"/>
     </row>
-    <row r="453" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="453" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="16">
         <v>213</v>
       </c>
@@ -43410,7 +43411,7 @@
       </c>
       <c r="K453" s="16"/>
     </row>
-    <row r="454" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="454" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="16">
         <v>214</v>
       </c>
@@ -43441,7 +43442,7 @@
       </c>
       <c r="K454" s="16"/>
     </row>
-    <row r="455" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="455" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="16">
         <v>215</v>
       </c>
@@ -43474,7 +43475,7 @@
         <v>2400</v>
       </c>
     </row>
-    <row r="456" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="456" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="16">
         <v>216</v>
       </c>
@@ -43505,7 +43506,7 @@
       </c>
       <c r="K456" s="16"/>
     </row>
-    <row r="457" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="457" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="16">
         <v>217</v>
       </c>
@@ -43536,7 +43537,7 @@
       </c>
       <c r="K457" s="16"/>
     </row>
-    <row r="458" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="458" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="16">
         <v>218</v>
       </c>
@@ -43567,7 +43568,7 @@
       </c>
       <c r="K458" s="16"/>
     </row>
-    <row r="459" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="459" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="16">
         <v>219</v>
       </c>
@@ -43598,7 +43599,7 @@
       </c>
       <c r="K459" s="16"/>
     </row>
-    <row r="460" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="460" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="16">
         <v>220</v>
       </c>
@@ -43629,7 +43630,7 @@
       </c>
       <c r="K460" s="16"/>
     </row>
-    <row r="461" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="461" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="16">
         <v>221</v>
       </c>
@@ -43660,7 +43661,7 @@
       </c>
       <c r="K461" s="16"/>
     </row>
-    <row r="462" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="462" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="16">
         <v>222</v>
       </c>
@@ -43691,7 +43692,7 @@
       </c>
       <c r="K462" s="16"/>
     </row>
-    <row r="463" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="463" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="16">
         <v>223</v>
       </c>
@@ -43722,7 +43723,7 @@
       </c>
       <c r="K463" s="16"/>
     </row>
-    <row r="464" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="464" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="16">
         <v>224</v>
       </c>
@@ -43753,7 +43754,7 @@
       </c>
       <c r="K464" s="16"/>
     </row>
-    <row r="465" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="465" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="16">
         <v>225</v>
       </c>
@@ -43784,7 +43785,7 @@
       </c>
       <c r="K465" s="16"/>
     </row>
-    <row r="466" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="466" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="16">
         <v>226</v>
       </c>
@@ -43815,7 +43816,7 @@
       </c>
       <c r="K466" s="16"/>
     </row>
-    <row r="467" spans="1:11" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="467" spans="1:11" ht="127.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="16">
         <v>227</v>
       </c>
@@ -43846,7 +43847,7 @@
       </c>
       <c r="K467" s="16"/>
     </row>
-    <row r="468" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="468" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="16">
         <v>228</v>
       </c>
@@ -43877,7 +43878,7 @@
       </c>
       <c r="K468" s="16"/>
     </row>
-    <row r="469" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="469" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="16">
         <v>229</v>
       </c>
@@ -43908,7 +43909,7 @@
       </c>
       <c r="K469" s="16"/>
     </row>
-    <row r="470" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="470" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="16">
         <v>230</v>
       </c>
@@ -43939,7 +43940,7 @@
       </c>
       <c r="K470" s="16"/>
     </row>
-    <row r="471" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="471" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="16">
         <v>231</v>
       </c>
@@ -43970,7 +43971,7 @@
       </c>
       <c r="K471" s="16"/>
     </row>
-    <row r="472" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="472" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="16">
         <v>232</v>
       </c>
@@ -44001,7 +44002,7 @@
       </c>
       <c r="K472" s="16"/>
     </row>
-    <row r="473" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="473" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="16">
         <v>233</v>
       </c>
@@ -44032,7 +44033,7 @@
       </c>
       <c r="K473" s="16"/>
     </row>
-    <row r="474" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="474" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="16">
         <v>234</v>
       </c>
@@ -44063,7 +44064,7 @@
       </c>
       <c r="K474" s="16"/>
     </row>
-    <row r="475" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="475" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="16">
         <v>235</v>
       </c>
@@ -44094,7 +44095,7 @@
       </c>
       <c r="K475" s="16"/>
     </row>
-    <row r="476" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="476" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="16">
         <v>236</v>
       </c>
@@ -44125,7 +44126,7 @@
       </c>
       <c r="K476" s="16"/>
     </row>
-    <row r="477" spans="1:11" ht="144" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:11" ht="144" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="16">
         <v>237</v>
       </c>
@@ -44156,7 +44157,7 @@
       </c>
       <c r="K477" s="16"/>
     </row>
-    <row r="478" spans="1:11" ht="192" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:11" ht="192" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="16">
         <v>238</v>
       </c>
@@ -44187,7 +44188,7 @@
       </c>
       <c r="K478" s="16"/>
     </row>
-    <row r="479" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="16">
         <v>239</v>
       </c>
@@ -44218,7 +44219,7 @@
       </c>
       <c r="K479" s="16"/>
     </row>
-    <row r="480" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="16">
         <v>240</v>
       </c>
@@ -44249,7 +44250,7 @@
       </c>
       <c r="K480" s="16"/>
     </row>
-    <row r="481" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="16">
         <v>241</v>
       </c>
@@ -44280,7 +44281,7 @@
       </c>
       <c r="K481" s="16"/>
     </row>
-    <row r="482" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="16">
         <v>242</v>
       </c>
@@ -44311,7 +44312,7 @@
       </c>
       <c r="K482" s="16"/>
     </row>
-    <row r="483" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="16">
         <v>243</v>
       </c>
@@ -44342,7 +44343,7 @@
       </c>
       <c r="K483" s="16"/>
     </row>
-    <row r="484" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="16">
         <v>244</v>
       </c>
@@ -44373,7 +44374,7 @@
       </c>
       <c r="K484" s="16"/>
     </row>
-    <row r="485" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="16">
         <v>245</v>
       </c>
@@ -44404,7 +44405,7 @@
       </c>
       <c r="K485" s="16"/>
     </row>
-    <row r="486" spans="1:11" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:11" ht="127.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="16">
         <v>246</v>
       </c>
@@ -44435,7 +44436,7 @@
       </c>
       <c r="K486" s="16"/>
     </row>
-    <row r="487" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="16">
         <v>247</v>
       </c>
@@ -44466,7 +44467,7 @@
       </c>
       <c r="K487" s="16"/>
     </row>
-    <row r="488" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="16">
         <v>248</v>
       </c>
@@ -44497,7 +44498,7 @@
       </c>
       <c r="K488" s="16"/>
     </row>
-    <row r="489" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="16">
         <v>249</v>
       </c>
@@ -44528,7 +44529,7 @@
       </c>
       <c r="K489" s="16"/>
     </row>
-    <row r="490" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="16">
         <v>250</v>
       </c>
@@ -44559,7 +44560,7 @@
       </c>
       <c r="K490" s="16"/>
     </row>
-    <row r="491" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="16">
         <v>251</v>
       </c>
@@ -44590,7 +44591,7 @@
       </c>
       <c r="K491" s="16"/>
     </row>
-    <row r="492" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="16">
         <v>252</v>
       </c>
@@ -44621,7 +44622,7 @@
       </c>
       <c r="K492" s="16"/>
     </row>
-    <row r="493" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="16">
         <v>253</v>
       </c>
@@ -44652,7 +44653,7 @@
       </c>
       <c r="K493" s="16"/>
     </row>
-    <row r="494" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="16">
         <v>254</v>
       </c>
@@ -44683,7 +44684,7 @@
       </c>
       <c r="K494" s="16"/>
     </row>
-    <row r="495" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="16">
         <v>255</v>
       </c>
@@ -44714,7 +44715,7 @@
       </c>
       <c r="K495" s="16"/>
     </row>
-    <row r="496" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="16">
         <v>256</v>
       </c>
@@ -44747,7 +44748,7 @@
         <v>2455</v>
       </c>
     </row>
-    <row r="497" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="16">
         <v>257</v>
       </c>
@@ -44778,7 +44779,7 @@
       </c>
       <c r="K497" s="16"/>
     </row>
-    <row r="498" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="16">
         <v>258</v>
       </c>
@@ -44809,7 +44810,7 @@
       </c>
       <c r="K498" s="16"/>
     </row>
-    <row r="499" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="16">
         <v>259</v>
       </c>
@@ -44840,7 +44841,7 @@
       </c>
       <c r="K499" s="16"/>
     </row>
-    <row r="500" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="16">
         <v>260</v>
       </c>
@@ -44871,7 +44872,7 @@
       </c>
       <c r="K500" s="16"/>
     </row>
-    <row r="501" spans="1:11" ht="175.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="501" spans="1:11" ht="175.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="16">
         <v>261</v>
       </c>
@@ -44902,7 +44903,7 @@
       </c>
       <c r="K501" s="16"/>
     </row>
-    <row r="502" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="502" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="16">
         <v>262</v>
       </c>
@@ -44933,7 +44934,7 @@
       </c>
       <c r="K502" s="16"/>
     </row>
-    <row r="503" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="503" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="16">
         <v>263</v>
       </c>
@@ -44964,7 +44965,7 @@
       </c>
       <c r="K503" s="16"/>
     </row>
-    <row r="504" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="504" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="16">
         <v>264</v>
       </c>
@@ -44995,7 +44996,7 @@
       </c>
       <c r="K504" s="16"/>
     </row>
-    <row r="505" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="505" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="16">
         <v>265</v>
       </c>
@@ -45026,7 +45027,7 @@
       </c>
       <c r="K505" s="16"/>
     </row>
-    <row r="506" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="506" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="16">
         <v>266</v>
       </c>
@@ -45057,7 +45058,7 @@
       </c>
       <c r="K506" s="16"/>
     </row>
-    <row r="507" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="507" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="16">
         <v>267</v>
       </c>
@@ -45088,7 +45089,7 @@
       </c>
       <c r="K507" s="16"/>
     </row>
-    <row r="508" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="508" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="16">
         <v>268</v>
       </c>
@@ -45119,7 +45120,7 @@
       </c>
       <c r="K508" s="16"/>
     </row>
-    <row r="509" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="509" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="16">
         <v>269</v>
       </c>
@@ -45150,7 +45151,7 @@
       </c>
       <c r="K509" s="16"/>
     </row>
-    <row r="510" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="510" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="16">
         <v>270</v>
       </c>
@@ -45181,7 +45182,7 @@
       </c>
       <c r="K510" s="16"/>
     </row>
-    <row r="511" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="511" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="16">
         <v>271</v>
       </c>
@@ -45247,7 +45248,7 @@
         <v>2359</v>
       </c>
     </row>
-    <row r="513" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="513" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="16">
         <v>184</v>
       </c>
@@ -45311,7 +45312,7 @@
       </c>
       <c r="K514" s="16"/>
     </row>
-    <row r="515" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="515" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="16">
         <v>186</v>
       </c>
@@ -45342,7 +45343,7 @@
       </c>
       <c r="K515" s="16"/>
     </row>
-    <row r="516" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="516" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="16">
         <v>187</v>
       </c>
@@ -45373,7 +45374,7 @@
       </c>
       <c r="K516" s="16"/>
     </row>
-    <row r="517" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="517" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="16">
         <v>188</v>
       </c>
@@ -45404,7 +45405,7 @@
       </c>
       <c r="K517" s="16"/>
     </row>
-    <row r="518" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="518" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="16">
         <v>189</v>
       </c>
@@ -45435,7 +45436,7 @@
       </c>
       <c r="K518" s="16"/>
     </row>
-    <row r="519" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="519" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="16">
         <v>190</v>
       </c>
@@ -45466,7 +45467,7 @@
       </c>
       <c r="K519" s="16"/>
     </row>
-    <row r="520" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="520" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="16">
         <v>191</v>
       </c>
@@ -45497,7 +45498,7 @@
       </c>
       <c r="K520" s="16"/>
     </row>
-    <row r="521" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="521" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="16">
         <v>192</v>
       </c>
@@ -45528,7 +45529,7 @@
       </c>
       <c r="K521" s="16"/>
     </row>
-    <row r="522" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="522" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="16">
         <v>193</v>
       </c>
@@ -45559,7 +45560,7 @@
       </c>
       <c r="K522" s="16"/>
     </row>
-    <row r="523" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="523" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="16">
         <v>194</v>
       </c>
@@ -45590,7 +45591,7 @@
       </c>
       <c r="K523" s="16"/>
     </row>
-    <row r="524" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="524" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="16">
         <v>195</v>
       </c>
@@ -45621,7 +45622,7 @@
       </c>
       <c r="K524" s="16"/>
     </row>
-    <row r="525" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="525" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="16">
         <v>196</v>
       </c>
@@ -45652,7 +45653,7 @@
       </c>
       <c r="K525" s="16"/>
     </row>
-    <row r="526" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="526" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="16">
         <v>197</v>
       </c>
@@ -45683,7 +45684,7 @@
       </c>
       <c r="K526" s="16"/>
     </row>
-    <row r="527" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="527" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="16">
         <v>198</v>
       </c>
@@ -45714,7 +45715,7 @@
       </c>
       <c r="K527" s="16"/>
     </row>
-    <row r="528" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="528" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="16">
         <v>199</v>
       </c>
@@ -45745,7 +45746,7 @@
       </c>
       <c r="K528" s="16"/>
     </row>
-    <row r="529" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="529" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="16">
         <v>200</v>
       </c>
@@ -45776,7 +45777,7 @@
       </c>
       <c r="K529" s="16"/>
     </row>
-    <row r="530" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="530" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="16">
         <v>201</v>
       </c>
@@ -45807,7 +45808,7 @@
       </c>
       <c r="K530" s="16"/>
     </row>
-    <row r="531" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="531" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="16">
         <v>202</v>
       </c>
@@ -45838,7 +45839,7 @@
       </c>
       <c r="K531" s="16"/>
     </row>
-    <row r="532" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="532" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="16">
         <v>203</v>
       </c>
@@ -45869,7 +45870,7 @@
       </c>
       <c r="K532" s="16"/>
     </row>
-    <row r="533" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="533" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="16">
         <v>204</v>
       </c>
@@ -45900,7 +45901,7 @@
       </c>
       <c r="K533" s="16"/>
     </row>
-    <row r="534" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="534" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="16">
         <v>205</v>
       </c>
@@ -45931,7 +45932,7 @@
       </c>
       <c r="K534" s="16"/>
     </row>
-    <row r="535" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="535" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="16">
         <v>206</v>
       </c>
@@ -45964,7 +45965,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="536" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="536" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="16">
         <v>207</v>
       </c>
@@ -46032,7 +46033,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="538" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="538" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="16">
         <v>165</v>
       </c>
@@ -46096,7 +46097,7 @@
       </c>
       <c r="K539" s="16"/>
     </row>
-    <row r="540" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="540" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="16">
         <v>167</v>
       </c>
@@ -46127,7 +46128,7 @@
       </c>
       <c r="K540" s="16"/>
     </row>
-    <row r="541" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="541" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="16">
         <v>168</v>
       </c>
@@ -46158,7 +46159,7 @@
       </c>
       <c r="K541" s="16"/>
     </row>
-    <row r="542" spans="1:11" ht="159.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="542" spans="1:11" ht="159.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="16">
         <v>169</v>
       </c>
@@ -46189,7 +46190,7 @@
       </c>
       <c r="K542" s="16"/>
     </row>
-    <row r="543" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="543" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="16">
         <v>170</v>
       </c>
@@ -46220,7 +46221,7 @@
       </c>
       <c r="K543" s="16"/>
     </row>
-    <row r="544" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="544" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="16">
         <v>171</v>
       </c>
@@ -46251,7 +46252,7 @@
       </c>
       <c r="K544" s="16"/>
     </row>
-    <row r="545" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="545" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="16">
         <v>172</v>
       </c>
@@ -46282,7 +46283,7 @@
       </c>
       <c r="K545" s="16"/>
     </row>
-    <row r="546" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="546" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="16">
         <v>173</v>
       </c>
@@ -46313,7 +46314,7 @@
       </c>
       <c r="K546" s="16"/>
     </row>
-    <row r="547" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="547" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="16">
         <v>174</v>
       </c>
@@ -46344,7 +46345,7 @@
       </c>
       <c r="K547" s="16"/>
     </row>
-    <row r="548" spans="1:11" ht="207.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="548" spans="1:11" ht="207.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="16">
         <v>175</v>
       </c>
@@ -46375,7 +46376,7 @@
       </c>
       <c r="K548" s="16"/>
     </row>
-    <row r="549" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="549" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="16">
         <v>176</v>
       </c>
@@ -46406,7 +46407,7 @@
       </c>
       <c r="K549" s="16"/>
     </row>
-    <row r="550" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="550" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="16">
         <v>177</v>
       </c>
@@ -46437,7 +46438,7 @@
       </c>
       <c r="K550" s="16"/>
     </row>
-    <row r="551" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="551" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="16">
         <v>178</v>
       </c>
@@ -46468,7 +46469,7 @@
       </c>
       <c r="K551" s="16"/>
     </row>
-    <row r="552" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="552" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="16">
         <v>179</v>
       </c>
@@ -46499,7 +46500,7 @@
       </c>
       <c r="K552" s="16"/>
     </row>
-    <row r="553" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="553" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="16">
         <v>180</v>
       </c>
@@ -46530,7 +46531,7 @@
       </c>
       <c r="K553" s="16"/>
     </row>
-    <row r="554" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="554" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="16">
         <v>181</v>
       </c>
@@ -46561,7 +46562,7 @@
       </c>
       <c r="K554" s="16"/>
     </row>
-    <row r="555" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="555" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="16">
         <v>182</v>
       </c>
@@ -46627,7 +46628,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="557" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="557" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="16">
         <v>152</v>
       </c>
@@ -46658,7 +46659,7 @@
       </c>
       <c r="K557" s="16"/>
     </row>
-    <row r="558" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="558" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="16">
         <v>153</v>
       </c>
@@ -46757,7 +46758,7 @@
       </c>
       <c r="K560" s="16"/>
     </row>
-    <row r="561" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="561" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="16">
         <v>156</v>
       </c>
@@ -46788,7 +46789,7 @@
       </c>
       <c r="K561" s="16"/>
     </row>
-    <row r="562" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="562" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="16">
         <v>157</v>
       </c>
@@ -46819,7 +46820,7 @@
       </c>
       <c r="K562" s="16"/>
     </row>
-    <row r="563" spans="1:11" ht="64.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="563" spans="1:11" ht="64.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="16">
         <v>158</v>
       </c>
@@ -46885,7 +46886,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="565" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="565" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="16">
         <v>140</v>
       </c>
@@ -46951,7 +46952,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="567" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="567" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="16">
         <v>142</v>
       </c>
@@ -46984,7 +46985,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="568" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="568" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="16">
         <v>143</v>
       </c>
@@ -47015,7 +47016,7 @@
       </c>
       <c r="K568" s="16"/>
     </row>
-    <row r="569" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="569" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="16">
         <v>144</v>
       </c>
@@ -47046,7 +47047,7 @@
       </c>
       <c r="K569" s="16"/>
     </row>
-    <row r="570" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="570" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="16">
         <v>145</v>
       </c>
@@ -47112,7 +47113,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="572" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="572" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="16">
         <v>147</v>
       </c>
@@ -47145,7 +47146,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="573" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="573" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="16">
         <v>148</v>
       </c>
@@ -47178,7 +47179,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="574" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="574" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="16">
         <v>149</v>
       </c>
@@ -47209,7 +47210,7 @@
       </c>
       <c r="K574" s="16"/>
     </row>
-    <row r="575" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="575" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="16">
         <v>150</v>
       </c>
@@ -47275,7 +47276,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="577" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="577" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="16">
         <v>125</v>
       </c>
@@ -47306,7 +47307,7 @@
       </c>
       <c r="K577" s="16"/>
     </row>
-    <row r="578" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="578" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="16">
         <v>126</v>
       </c>
@@ -47469,7 +47470,7 @@
       </c>
       <c r="K582" s="16"/>
     </row>
-    <row r="583" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="583" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="16">
         <v>131</v>
       </c>
@@ -47500,7 +47501,7 @@
       </c>
       <c r="K583" s="16"/>
     </row>
-    <row r="584" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="584" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="16">
         <v>132</v>
       </c>
@@ -47531,7 +47532,7 @@
       </c>
       <c r="K584" s="16"/>
     </row>
-    <row r="585" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="585" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="16">
         <v>133</v>
       </c>
@@ -47562,7 +47563,7 @@
       </c>
       <c r="K585" s="16"/>
     </row>
-    <row r="586" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="586" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="16">
         <v>134</v>
       </c>
@@ -47593,7 +47594,7 @@
       </c>
       <c r="K586" s="16"/>
     </row>
-    <row r="587" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="587" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="16">
         <v>135</v>
       </c>
@@ -47624,7 +47625,7 @@
       </c>
       <c r="K587" s="16"/>
     </row>
-    <row r="588" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="588" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="16">
         <v>136</v>
       </c>
@@ -47655,7 +47656,7 @@
       </c>
       <c r="K588" s="16"/>
     </row>
-    <row r="589" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="589" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="16">
         <v>137</v>
       </c>
@@ -47686,7 +47687,7 @@
       </c>
       <c r="K589" s="16"/>
     </row>
-    <row r="590" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="590" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="16">
         <v>138</v>
       </c>
@@ -47752,7 +47753,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="592" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="592" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="16">
         <v>113</v>
       </c>
@@ -47816,7 +47817,7 @@
       </c>
       <c r="K593" s="16"/>
     </row>
-    <row r="594" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="594" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="16">
         <v>115</v>
       </c>
@@ -47847,7 +47848,7 @@
       </c>
       <c r="K594" s="16"/>
     </row>
-    <row r="595" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="595" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="16">
         <v>116</v>
       </c>
@@ -47878,7 +47879,7 @@
       </c>
       <c r="K595" s="16"/>
     </row>
-    <row r="596" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="596" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="16">
         <v>117</v>
       </c>
@@ -47909,7 +47910,7 @@
       </c>
       <c r="K596" s="16"/>
     </row>
-    <row r="597" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="597" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="16">
         <v>118</v>
       </c>
@@ -47940,7 +47941,7 @@
       </c>
       <c r="K597" s="16"/>
     </row>
-    <row r="598" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="598" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="16">
         <v>119</v>
       </c>
@@ -47971,7 +47972,7 @@
       </c>
       <c r="K598" s="16"/>
     </row>
-    <row r="599" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="599" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="16">
         <v>120</v>
       </c>
@@ -48002,7 +48003,7 @@
       </c>
       <c r="K599" s="16"/>
     </row>
-    <row r="600" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="600" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="16">
         <v>121</v>
       </c>
@@ -48033,7 +48034,7 @@
       </c>
       <c r="K600" s="16"/>
     </row>
-    <row r="601" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="601" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="16">
         <v>122</v>
       </c>
@@ -48064,7 +48065,7 @@
       </c>
       <c r="K601" s="16"/>
     </row>
-    <row r="602" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="602" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="16">
         <v>123</v>
       </c>
@@ -48130,7 +48131,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="604" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="604" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="16">
         <v>92</v>
       </c>
@@ -48194,7 +48195,7 @@
       </c>
       <c r="K605" s="16"/>
     </row>
-    <row r="606" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="606" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="16">
         <v>94</v>
       </c>
@@ -48225,7 +48226,7 @@
       </c>
       <c r="K606" s="16"/>
     </row>
-    <row r="607" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="607" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="16">
         <v>95</v>
       </c>
@@ -48256,7 +48257,7 @@
       </c>
       <c r="K607" s="16"/>
     </row>
-    <row r="608" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="608" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="16">
         <v>96</v>
       </c>
@@ -48287,7 +48288,7 @@
       </c>
       <c r="K608" s="16"/>
     </row>
-    <row r="609" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="609" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="16">
         <v>97</v>
       </c>
@@ -48318,7 +48319,7 @@
       </c>
       <c r="K609" s="16"/>
     </row>
-    <row r="610" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="610" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="16">
         <v>98</v>
       </c>
@@ -48349,7 +48350,7 @@
       </c>
       <c r="K610" s="16"/>
     </row>
-    <row r="611" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="611" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="16">
         <v>99</v>
       </c>
@@ -48380,7 +48381,7 @@
       </c>
       <c r="K611" s="16"/>
     </row>
-    <row r="612" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="612" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="16">
         <v>100</v>
       </c>
@@ -48411,7 +48412,7 @@
       </c>
       <c r="K612" s="16"/>
     </row>
-    <row r="613" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="613" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="16">
         <v>101</v>
       </c>
@@ -48442,7 +48443,7 @@
       </c>
       <c r="K613" s="16"/>
     </row>
-    <row r="614" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="614" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="16">
         <v>102</v>
       </c>
@@ -48473,7 +48474,7 @@
       </c>
       <c r="K614" s="16"/>
     </row>
-    <row r="615" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="615" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="16">
         <v>103</v>
       </c>
@@ -48504,7 +48505,7 @@
       </c>
       <c r="K615" s="16"/>
     </row>
-    <row r="616" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="616" spans="1:11" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="16">
         <v>104</v>
       </c>
@@ -48535,7 +48536,7 @@
       </c>
       <c r="K616" s="16"/>
     </row>
-    <row r="617" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="617" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="16">
         <v>105</v>
       </c>
@@ -48566,7 +48567,7 @@
       </c>
       <c r="K617" s="16"/>
     </row>
-    <row r="618" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="618" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="16">
         <v>106</v>
       </c>
@@ -48597,7 +48598,7 @@
       </c>
       <c r="K618" s="16"/>
     </row>
-    <row r="619" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="619" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="16">
         <v>107</v>
       </c>
@@ -48628,7 +48629,7 @@
       </c>
       <c r="K619" s="16"/>
     </row>
-    <row r="620" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="620" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="16">
         <v>108</v>
       </c>
@@ -48659,7 +48660,7 @@
       </c>
       <c r="K620" s="16"/>
     </row>
-    <row r="621" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="621" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="16">
         <v>109</v>
       </c>
@@ -48690,7 +48691,7 @@
       </c>
       <c r="K621" s="16"/>
     </row>
-    <row r="622" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="622" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="16">
         <v>110</v>
       </c>
@@ -48721,7 +48722,7 @@
       </c>
       <c r="K622" s="16"/>
     </row>
-    <row r="623" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="623" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="16">
         <v>111</v>
       </c>
@@ -48787,7 +48788,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="625" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="625" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="16">
         <v>26</v>
       </c>
@@ -48820,7 +48821,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="626" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="626" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="16">
         <v>27</v>
       </c>
@@ -48853,7 +48854,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="627" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="627" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="16">
         <v>28</v>
       </c>
@@ -48886,7 +48887,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="628" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="628" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="16">
         <v>29</v>
       </c>
@@ -48919,7 +48920,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="629" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="629" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="16">
         <v>30</v>
       </c>
@@ -48952,7 +48953,7 @@
         <v>2048</v>
       </c>
     </row>
-    <row r="630" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="630" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="16">
         <v>31</v>
       </c>
@@ -48985,7 +48986,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="631" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="631" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="16">
         <v>32</v>
       </c>
@@ -49018,7 +49019,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="632" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="632" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="16">
         <v>33</v>
       </c>
@@ -49051,7 +49052,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="633" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="633" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="16">
         <v>34</v>
       </c>
@@ -49084,7 +49085,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="634" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="634" spans="1:11" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="16">
         <v>35</v>
       </c>
@@ -49117,7 +49118,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="635" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="635" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="16">
         <v>36</v>
       </c>
@@ -49150,7 +49151,7 @@
         <v>2072</v>
       </c>
     </row>
-    <row r="636" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="636" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="16">
         <v>37</v>
       </c>
@@ -49183,7 +49184,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="637" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="637" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="16">
         <v>38</v>
       </c>
@@ -49216,7 +49217,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="638" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="638" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="16">
         <v>39</v>
       </c>
@@ -49249,7 +49250,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="639" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="639" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="16">
         <v>40</v>
       </c>
@@ -49282,7 +49283,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="640" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="640" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="16">
         <v>41</v>
       </c>
@@ -49315,7 +49316,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="641" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="641" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="16">
         <v>42</v>
       </c>
@@ -49348,7 +49349,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="642" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="642" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="16">
         <v>43</v>
       </c>
@@ -49381,7 +49382,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="643" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="643" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="16">
         <v>44</v>
       </c>
@@ -49414,7 +49415,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="644" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="644" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="16">
         <v>45</v>
       </c>
@@ -49447,7 +49448,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="645" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="645" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="16">
         <v>46</v>
       </c>
@@ -49480,7 +49481,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="646" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="646" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="16">
         <v>47</v>
       </c>
@@ -49513,7 +49514,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="647" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="647" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="16">
         <v>48</v>
       </c>
@@ -49546,7 +49547,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="648" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="648" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="16">
         <v>49</v>
       </c>
@@ -49579,7 +49580,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="649" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="649" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="16">
         <v>50</v>
       </c>
@@ -49610,7 +49611,7 @@
       </c>
       <c r="K649" s="16"/>
     </row>
-    <row r="650" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="650" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="16">
         <v>51</v>
       </c>
@@ -49643,7 +49644,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="651" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="651" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="16">
         <v>52</v>
       </c>
@@ -49676,7 +49677,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="652" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="652" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="16">
         <v>53</v>
       </c>
@@ -49709,7 +49710,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="653" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="653" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="16">
         <v>54</v>
       </c>
@@ -49742,7 +49743,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="654" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="654" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="16">
         <v>55</v>
       </c>
@@ -49773,7 +49774,7 @@
       </c>
       <c r="K654" s="16"/>
     </row>
-    <row r="655" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="655" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="16">
         <v>56</v>
       </c>
@@ -49806,7 +49807,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="656" spans="1:11" ht="394.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="656" spans="1:11" ht="394.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="16">
         <v>57</v>
       </c>
@@ -49839,7 +49840,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="657" spans="1:11" ht="207.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="657" spans="1:11" ht="207.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="16">
         <v>58</v>
       </c>
@@ -49872,7 +49873,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="658" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="658" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="16">
         <v>59</v>
       </c>
@@ -49905,7 +49906,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="659" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="659" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="16">
         <v>60</v>
       </c>
@@ -49936,7 +49937,7 @@
       </c>
       <c r="K659" s="16"/>
     </row>
-    <row r="660" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="660" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="16">
         <v>61</v>
       </c>
@@ -49969,7 +49970,7 @@
         <v>2149</v>
       </c>
     </row>
-    <row r="661" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="661" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="16">
         <v>62</v>
       </c>
@@ -50002,7 +50003,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="662" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="662" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="16">
         <v>63</v>
       </c>
@@ -50035,7 +50036,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="663" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="663" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="16">
         <v>64</v>
       </c>
@@ -50068,7 +50069,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="664" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="664" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="16">
         <v>65</v>
       </c>
@@ -50099,7 +50100,7 @@
       </c>
       <c r="K664" s="16"/>
     </row>
-    <row r="665" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="665" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="16">
         <v>66</v>
       </c>
@@ -50132,7 +50133,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="666" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="666" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="16">
         <v>67</v>
       </c>
@@ -50165,7 +50166,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="667" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="667" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="16">
         <v>68</v>
       </c>
@@ -50198,7 +50199,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="668" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="668" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="16">
         <v>69</v>
       </c>
@@ -50231,7 +50232,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="669" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="669" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="16">
         <v>70</v>
       </c>
@@ -50262,7 +50263,7 @@
       </c>
       <c r="K669" s="16"/>
     </row>
-    <row r="670" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="670" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="16">
         <v>71</v>
       </c>
@@ -50295,7 +50296,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="671" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="671" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="16">
         <v>72</v>
       </c>
@@ -50328,7 +50329,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="672" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="672" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="16">
         <v>73</v>
       </c>
@@ -50361,7 +50362,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="673" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="673" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="16">
         <v>74</v>
       </c>
@@ -50394,7 +50395,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="674" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="674" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="16">
         <v>75</v>
       </c>
@@ -50425,7 +50426,7 @@
       </c>
       <c r="K674" s="16"/>
     </row>
-    <row r="675" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="675" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="16">
         <v>76</v>
       </c>
@@ -50458,7 +50459,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="676" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="676" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="16">
         <v>77</v>
       </c>
@@ -50491,7 +50492,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="677" spans="1:11" ht="96" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="677" spans="1:11" ht="96" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="16">
         <v>78</v>
       </c>
@@ -50524,7 +50525,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="678" spans="1:11" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="678" spans="1:11" ht="127.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="16">
         <v>79</v>
       </c>
@@ -50557,7 +50558,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="679" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="679" spans="1:11" ht="63.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="16">
         <v>80</v>
       </c>
@@ -50590,7 +50591,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="680" spans="1:11" ht="79.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="680" spans="1:11" ht="79.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="16">
         <v>81</v>
       </c>
@@ -50621,7 +50622,7 @@
       </c>
       <c r="K680" s="16"/>
     </row>
-    <row r="681" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="681" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="16">
         <v>82</v>
       </c>
@@ -50654,7 +50655,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="682" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="682" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="16">
         <v>83</v>
       </c>
@@ -50687,7 +50688,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="683" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="683" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="16">
         <v>84</v>
       </c>
@@ -50720,7 +50721,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="684" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="684" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="16">
         <v>85</v>
       </c>
@@ -50753,7 +50754,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="685" spans="1:11" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="685" spans="1:11" ht="48" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="16">
         <v>86</v>
       </c>
@@ -50786,7 +50787,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="686" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="686" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="16">
         <v>87</v>
       </c>
@@ -50819,7 +50820,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="687" spans="1:11" ht="127.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="687" spans="1:11" ht="127.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="16">
         <v>88</v>
       </c>
@@ -50852,7 +50853,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="688" spans="1:11" ht="111.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="688" spans="1:11" ht="111.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="16">
         <v>89</v>
       </c>
@@ -50885,7 +50886,7 @@
         <v>2043</v>
       </c>
     </row>
-    <row r="689" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="689" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="16">
         <v>90</v>
       </c>
@@ -50949,7 +50950,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="691" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="691" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="16">
         <v>22</v>
       </c>
@@ -50982,7 +50983,7 @@
         <v>2010</v>
       </c>
     </row>
-    <row r="692" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="692" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="16">
         <v>23</v>
       </c>
@@ -51015,7 +51016,7 @@
         <v>2014</v>
       </c>
     </row>
-    <row r="693" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="693" spans="1:11" ht="31.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="16">
         <v>24</v>
       </c>
@@ -51081,7 +51082,7 @@
       </c>
       <c r="K694" s="16"/>
     </row>
-    <row r="695" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="695" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="16">
         <v>2</v>
       </c>
@@ -51281,7 +51282,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="701" spans="1:11" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="701" spans="1:11" ht="115.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="16">
         <v>8</v>
       </c>
@@ -51314,7 +51315,7 @@
         <v>1928</v>
       </c>
     </row>
-    <row r="702" spans="1:11" ht="115.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="702" spans="1:11" ht="115.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="16">
         <v>9</v>
       </c>
@@ -51347,7 +51348,7 @@
         <v>1933</v>
       </c>
     </row>
-    <row r="703" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="703" spans="1:11" ht="90" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="16">
         <v>10</v>
       </c>
@@ -51380,7 +51381,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="704" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="704" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="16">
         <v>11</v>
       </c>
@@ -51413,7 +51414,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="705" spans="1:11" ht="77.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="705" spans="1:11" ht="77.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="16">
         <v>12</v>
       </c>
@@ -51446,7 +51447,7 @@
         <v>1954</v>
       </c>
     </row>
-    <row r="706" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="706" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="16">
         <v>13</v>
       </c>
@@ -51479,7 +51480,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="707" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="707" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="16">
         <v>14</v>
       </c>
@@ -51512,7 +51513,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="708" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="708" spans="1:11" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="16">
         <v>15</v>
       </c>
@@ -51545,7 +51546,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="709" spans="1:11" ht="178.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="709" spans="1:11" ht="178.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="16">
         <v>16</v>
       </c>
@@ -51578,7 +51579,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="710" spans="1:11" ht="409.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="710" spans="1:11" ht="409.5" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="16">
         <v>17</v>
       </c>
@@ -51611,7 +51612,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="711" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="711" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="16">
         <v>18</v>
       </c>
@@ -51644,7 +51645,7 @@
         <v>1990</v>
       </c>
     </row>
-    <row r="712" spans="1:11" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="712" spans="1:11" ht="39" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="16">
         <v>19</v>
       </c>
@@ -51677,7 +51678,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="713" spans="1:11" ht="51.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="713" spans="1:11" ht="51.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="16">
         <v>20</v>
       </c>
@@ -51711,7 +51712,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K713" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A1:K713" xr:uid="{00000000-0001-0000-0200-000000000000}">
+    <filterColumn colId="3">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
